--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Varberg BoIS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0 x 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>95.8</v>
+        <v>98.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,30 +514,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 x 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,18 +546,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>76.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -565,17 +565,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,18 +589,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>97</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -608,17 +608,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>92.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,97 +675,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>94</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
           <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -817,16 +731,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="C2" t="n">
-        <v>1195</v>
+        <v>1228</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.42</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="3">
@@ -836,16 +750,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C3" t="n">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>98.14</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +769,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>95.65000000000001</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="5">
@@ -874,16 +788,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -893,16 +807,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>85.70999999999999</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="7">
@@ -912,10 +826,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -931,10 +845,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -950,16 +864,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -972,13 +886,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1045,13 +959,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1064,13 +978,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1083,13 +997,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1102,13 +1016,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,12 +484,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,181 +503,9 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>98.2</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sweden Superettan</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>GIF Sundsvall</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -731,16 +559,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1239</v>
+        <v>1231</v>
       </c>
       <c r="C2" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>99.11</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -750,16 +578,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C3" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>97.38</v>
+        <v>97.12</v>
       </c>
     </row>
     <row r="4">
@@ -769,16 +597,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>98.55</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -807,16 +635,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>94.44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -826,10 +654,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -883,16 +711,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -959,13 +787,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -978,13 +806,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -997,13 +825,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1016,13 +844,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Waterford United</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,11 +503,398 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>96.39999999999999</v>
+        <v>88</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>St Patrick's</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wexford Youths</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>84</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>91</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -559,16 +946,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1231</v>
+        <v>1257</v>
       </c>
       <c r="C2" t="n">
-        <v>1223</v>
+        <v>1250</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>99.34999999999999</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="3">
@@ -578,16 +965,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C3" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>97.12</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="4">
@@ -597,16 +984,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>97.40000000000001</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="5">
@@ -616,16 +1003,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="6">
@@ -635,16 +1022,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -692,16 +1079,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -787,13 +1174,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -806,13 +1193,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -825,13 +1212,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -844,13 +1231,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Waterford United</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St Patrick's</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>99.8</v>
+        <v>63.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>60-65%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>82.8</v>
+        <v>99</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>91.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>94.19999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>84</v>
+        <v>92.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -733,21 +733,21 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,140 +761,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>91</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Kerry</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Athlone Town</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Finn Harps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>UCD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>89.60000000000001</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -946,16 +817,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1257</v>
+        <v>1309</v>
       </c>
       <c r="C2" t="n">
-        <v>1250</v>
+        <v>1297</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>99.44</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="3">
@@ -965,16 +836,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="C3" t="n">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>96.75</v>
+        <v>97.47</v>
       </c>
     </row>
     <row r="4">
@@ -984,16 +855,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>95.77</v>
+        <v>95.89</v>
       </c>
     </row>
     <row r="5">
@@ -1003,16 +874,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>97.22</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="6">
@@ -1022,16 +893,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1041,10 +912,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1079,13 +950,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1098,16 +969,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="11">
@@ -1155,13 +1026,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1174,13 +1045,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1193,13 +1064,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>63.2</v>
+        <v>90.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>92.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>92.2</v>
+        <v>99.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>92.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,11 +761,570 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>94.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Strømmen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>95</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hødd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ranheim</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>95</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>87</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>92</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Keflavík</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -817,16 +1376,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1309</v>
+        <v>1267</v>
       </c>
       <c r="C2" t="n">
-        <v>1297</v>
+        <v>1256</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.08</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="3">
@@ -836,16 +1395,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="C3" t="n">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>97.47</v>
+        <v>97.73</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +1414,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>95.89</v>
+        <v>95.70999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -874,16 +1433,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>92.86</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="6">
@@ -893,16 +1452,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="7">
@@ -931,10 +1490,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -950,16 +1509,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -969,16 +1528,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1026,13 +1585,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1045,13 +1604,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1064,13 +1623,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1083,13 +1642,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1102,13 +1661,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +475,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>98.59999999999999</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -518,21 +518,21 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg BoIS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>83.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,654 +675,9 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>99.2</v>
+        <v>95.8</v>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Strømsgodset</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Raufoss</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stabæk</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Egersund</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sogndal</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Moss</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sandnes Ulf</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Strømmen</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Lyn</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bryne</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>95</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Hødd</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Kongsvinger</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Haugesund</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ranheim</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75-80%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>95</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>87</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>92</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Náutico</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>80-85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Thór</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ÍBV</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Keflavík</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>FH</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -1376,16 +731,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1267</v>
+        <v>1253</v>
       </c>
       <c r="C2" t="n">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>99.13</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1395,16 +750,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="C3" t="n">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>97.73</v>
+        <v>98.53</v>
       </c>
     </row>
     <row r="4">
@@ -1414,16 +769,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>95.70999999999999</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="5">
@@ -1433,16 +788,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.3</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="6">
@@ -1452,16 +807,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>93.75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1471,16 +826,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1490,10 +845,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1585,13 +940,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1604,13 +959,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1623,13 +978,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1642,13 +997,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1661,13 +1016,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1680,13 +1035,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,12 +484,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>97.39999999999999</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -518,21 +518,21 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>91.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,21 +561,21 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR Reykjavík</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>98</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>65-70%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,52 +632,95 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>98</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ÍA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B7" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>95.8</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -731,10 +774,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1253</v>
+        <v>1240</v>
       </c>
       <c r="C2" t="n">
-        <v>1248</v>
+        <v>1235</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -750,16 +793,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="C3" t="n">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>98.53</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="4">
@@ -769,16 +812,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>94.19</v>
+        <v>97.65000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -788,16 +831,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.67</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="6">
@@ -807,16 +850,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="7">
@@ -826,16 +869,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -864,16 +907,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -940,13 +983,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -959,13 +1002,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -978,13 +1021,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -997,13 +1040,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1016,13 +1059,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1035,13 +1078,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93.60000000000001</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>65-70%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.8</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KR Reykjavík</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>65.60000000000001</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>90.60000000000001</v>
+        <v>79</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,54 +675,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -774,16 +731,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1240</v>
+        <v>1303</v>
       </c>
       <c r="C2" t="n">
-        <v>1235</v>
+        <v>1290</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>99.59999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -793,16 +750,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="C3" t="n">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>98.3</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -812,16 +769,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>97.65000000000001</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="5">
@@ -831,16 +788,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>96.55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -850,16 +807,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>92.86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -869,10 +826,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -983,13 +940,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1002,13 +959,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1021,13 +978,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1040,13 +997,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1078,13 +1035,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +475,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>06:59:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69.39999999999999</v>
+        <v>99</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.19999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>92.80000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>99.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,11 +675,54 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>88.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Korea Republic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60-65%</t>
         </is>
       </c>
     </row>
@@ -731,16 +774,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1303</v>
+        <v>1276</v>
       </c>
       <c r="C2" t="n">
-        <v>1290</v>
+        <v>1266</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="3">
@@ -750,16 +793,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>97.48999999999999</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="4">
@@ -769,16 +812,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>97.22</v>
+        <v>95.23999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -807,16 +850,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="7">
@@ -826,10 +869,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -845,10 +888,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -864,16 +907,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="10">
@@ -883,16 +926,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -959,13 +1002,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -978,13 +1021,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -997,13 +1040,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1016,13 +1059,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1035,13 +1078,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,178 +551,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60-65%</t>
         </is>
       </c>
     </row>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06:59:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Waterford United</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,11 +546,398 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>86.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>St Patrick's</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>99</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Wexford Youths</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -602,16 +989,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1276</v>
+        <v>1300</v>
       </c>
       <c r="C2" t="n">
-        <v>1266</v>
+        <v>1290</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99.22</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="3">
@@ -621,16 +1008,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="C3" t="n">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>97.91</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="4">
@@ -640,16 +1027,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>95.23999999999999</v>
+        <v>97.83</v>
       </c>
     </row>
     <row r="5">
@@ -659,10 +1046,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -678,16 +1065,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>88.89</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="7">
@@ -697,10 +1084,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -716,10 +1103,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -735,16 +1122,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -773,13 +1160,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -811,13 +1198,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -830,13 +1217,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -868,13 +1255,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -887,13 +1274,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>97.59999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Waterford United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>St Patrick's</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,355 +589,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>97.2</v>
+        <v>84.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Republic of Ireland Premier Division</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Galway United</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Derry City</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Republic of Ireland Premier Division</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Drogheda United</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Shelbourne</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>99</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Republic of Ireland Premier Division</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bohemians</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Dundalk</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
           <t>80-85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UCD</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Kerry</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Cork City</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Treaty United</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Cobh Ramblers</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Finn Harps</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bray Wanderers</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Longford Town</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>92.80000000000001</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Athlone Town</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Wexford Youths</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -989,16 +645,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1300</v>
+        <v>1312</v>
       </c>
       <c r="C2" t="n">
-        <v>1290</v>
+        <v>1301</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.23</v>
+        <v>99.16</v>
       </c>
     </row>
     <row r="3">
@@ -1008,16 +664,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C3" t="n">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>96.25</v>
+        <v>97.81</v>
       </c>
     </row>
     <row r="4">
@@ -1027,16 +683,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>97.83</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1046,10 +702,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1065,16 +721,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="7">
@@ -1084,10 +740,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1103,10 +759,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1141,16 +797,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1160,13 +816,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1198,13 +854,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1217,13 +873,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1236,13 +892,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1255,13 +911,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1274,13 +930,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1293,13 +949,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>95.19999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,54 +546,828 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GIF Sundsvall</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Norrby</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>United Nordic</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>99</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Strømmen</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Stabæk</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>99</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Odd</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Hødd</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>90.60000000000001</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Åsane</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80-85%</t>
+      <c r="B14" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>74</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KA Akureyri</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Keflavík</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -645,16 +1419,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1312</v>
+        <v>1291</v>
       </c>
       <c r="C2" t="n">
-        <v>1301</v>
+        <v>1284</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>99.16</v>
+        <v>99.45999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +1438,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C3" t="n">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>97.81</v>
+        <v>97.73</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +1457,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>95.34999999999999</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="5">
@@ -702,16 +1476,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="6">
@@ -721,16 +1495,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>83.33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -759,10 +1533,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -873,13 +1647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -892,13 +1666,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -911,13 +1685,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -930,13 +1704,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -949,13 +1723,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +475,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg BoIS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>96.2</v>
+        <v>93.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -518,21 +518,21 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>98.40000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,21 +561,21 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>91.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,25 +600,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>98.8</v>
+        <v>97</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>99</v>
+        <v>93.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>KR Reykjavík</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -729,25 +729,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,611 +761,9 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Odd</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Hødd</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Moss</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sandnes Ulf</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>90.60000000000001</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Kongsvinger</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Strømsgodset</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Egersund</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Haugesund</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bryne</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Åsane</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>74</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ÍBV</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Stjarnan</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>KA Akureyri</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Valur</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Keflavík</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FH</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Thór</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>17:15:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fram</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Víkingur Reykjavík</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>90-95%</t>
         </is>
@@ -1419,16 +817,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1291</v>
+        <v>1354</v>
       </c>
       <c r="C2" t="n">
-        <v>1284</v>
+        <v>1343</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.45999999999999</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="3">
@@ -1438,16 +836,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C3" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>97.73</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="4">
@@ -1457,16 +855,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>97.03</v>
+        <v>94.37</v>
       </c>
     </row>
     <row r="5">
@@ -1476,16 +874,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>91.67</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="6">
@@ -1495,16 +893,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -1514,10 +912,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1533,10 +931,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1552,16 +950,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1628,13 +1026,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1647,13 +1045,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1666,13 +1064,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1685,13 +1083,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1704,13 +1102,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1723,13 +1121,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>95.19999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>94.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
+        <v>91.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KR Reykjavík</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>98.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -742,12 +742,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>90.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1354</v>
+        <v>1317</v>
       </c>
       <c r="C2" t="n">
-        <v>1343</v>
+        <v>1307</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99.19</v>
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="C3" t="n">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>97.75</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +855,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>94.37</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="5">
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>96.55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,226 +546,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96.8</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Finland Veikkausliiga</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KuPS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ilves</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Finland Veikkausliiga</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Inter Turku</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SJK</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Finland Veikkausliiga</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Jaro</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Gnistan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Finland Veikkausliiga</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mariehamn</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HJK</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>80-85%</t>
         </is>
       </c>
     </row>
@@ -817,16 +602,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1317</v>
+        <v>1369</v>
       </c>
       <c r="C2" t="n">
-        <v>1307</v>
+        <v>1357</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>99.23999999999999</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="3">
@@ -836,16 +621,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="C3" t="n">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>97.08</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +640,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>98.7</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -874,16 +659,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" t="n">
         <v>25</v>
       </c>
-      <c r="C5" t="n">
-        <v>22</v>
-      </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -896,13 +681,13 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="7">
@@ -931,16 +716,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -950,16 +735,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -969,13 +754,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1045,13 +830,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1064,13 +849,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,52 +503,482 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>92.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brage</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>94</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Waterford United</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>St Patrick's</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>96</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wexford Youths</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>95.39999999999999</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="B13" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -602,16 +1032,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1369</v>
+        <v>1355</v>
       </c>
       <c r="C2" t="n">
-        <v>1357</v>
+        <v>1346</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>99.12</v>
+        <v>99.34</v>
       </c>
     </row>
     <row r="3">
@@ -621,16 +1051,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="C3" t="n">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="4">
@@ -640,16 +1070,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>91.76000000000001</v>
+        <v>94.59</v>
       </c>
     </row>
     <row r="5">
@@ -659,16 +1089,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.15000000000001</v>
+        <v>95.23999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -678,16 +1108,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>90.91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -697,16 +1127,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="8">
@@ -716,16 +1146,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -735,16 +1165,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -754,13 +1184,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -811,13 +1241,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -830,13 +1260,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -849,13 +1279,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>97.59999999999999</v>
+        <v>83.39999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>99.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Waterford United</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>99.2</v>
+        <v>94</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>99.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St Patrick's</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>96</v>
+        <v>90.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>93.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shanghai Port</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>83.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -858,25 +858,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>97.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Chongqing Tonglianglong FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Tianjin Jinmen Tiger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,52 +933,654 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>93.60000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Varberg BoIS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Öster</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ljungskile</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>United Nordic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Oddevold</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GIF Sundsvall</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Åsane</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ranheim</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Strømmen</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>99</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stabæk</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>95</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>94</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Hødd</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>94</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Odd</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>97</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>93</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="B25" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -1032,16 +1634,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1355</v>
+        <v>1371</v>
       </c>
       <c r="C2" t="n">
-        <v>1346</v>
+        <v>1358</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>99.34</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="3">
@@ -1051,16 +1653,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C3" t="n">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>96.7</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="4">
@@ -1070,16 +1672,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>94.59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
@@ -1092,13 +1694,13 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>95.23999999999999</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="6">
@@ -1127,16 +1729,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1165,16 +1767,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1241,13 +1843,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1260,13 +1862,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1279,13 +1881,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1298,13 +1900,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Zhejiang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>83.39999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>95.59999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>88.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Liaoning Tieren FC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Taishan</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93.2</v>
+        <v>96</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shenzhen Peng City</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>98.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -815,25 +815,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Port</t>
+          <t>KR Reykjavík</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>81.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>98</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>95.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -944,25 +944,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>96.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -987,25 +987,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96.8</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,527 +1062,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94.8</v>
+        <v>89.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sweden Superettan</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>GIF Sundsvall</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Östersunds FK</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Åsane</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Ranheim</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Strømmen</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Moss</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>99</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stabæk</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Bryne</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>95</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sandnes Ulf</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Raufoss</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>94</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Lyn</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Hødd</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Haugesund</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Kongsvinger</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>94</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Strømsgodset</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Odd</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>97</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sogndal</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Egersund</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>93</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>80-85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>96.39999999999999</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Republic of Ireland Premier Division</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Sligo Rovers</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Shelbourne</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -1634,16 +1118,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1371</v>
+        <v>1399</v>
       </c>
       <c r="C2" t="n">
-        <v>1358</v>
+        <v>1385</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>99.05</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -1653,16 +1137,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C3" t="n">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>97.44</v>
+        <v>97.31999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1672,16 +1156,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="5">
@@ -1691,16 +1175,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>90.48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1729,10 +1213,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1748,10 +1232,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1767,16 +1251,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1805,13 +1289,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1843,13 +1327,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1862,13 +1346,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1881,13 +1365,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1900,13 +1384,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46201</v>
+        <v>46203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Qingdao West Coast</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zhejiang</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,570 +503,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>87.2</v>
+        <v>95.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>China PR Super League</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Dalian Yingbo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Shanghai Shenhua</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>94.19999999999999</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sweden Superettan</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Norrby</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>94</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sweden Superettan</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Landskrona</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Värnamo</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>90.60000000000001</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sweden Superettan</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sandviken</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Helsingborg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>98</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
           <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stjarnan</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>KA Akureyri</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>FH</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ÍBV</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>96</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Thór</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Valur</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Keflavík</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>KR Reykjavík</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>95.39999999999999</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Náutico</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>95.19999999999999</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -1118,16 +559,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1399</v>
+        <v>1424</v>
       </c>
       <c r="C2" t="n">
-        <v>1385</v>
+        <v>1416</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="3">
@@ -1137,16 +578,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C3" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>97.31999999999999</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="4">
@@ -1156,16 +597,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>95.12</v>
+        <v>90.14</v>
       </c>
     </row>
     <row r="5">
@@ -1175,10 +616,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1194,10 +635,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1232,10 +673,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1289,13 +730,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1327,13 +768,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1346,13 +787,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1365,13 +806,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1384,13 +825,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,43 +471,1032 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Korea Republic K-League 1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Korea Republic K-League 1</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>82.19999999999999</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Korea Republic K-League 1</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>China PR Super League</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Qingdao West Coast</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Shanghai Port</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China PR Super League</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Liaoning Tieren FC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chongqing Tonglianglong FC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>China PR Super League</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>08:35:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dalian Yingbo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Wuhan Three Towns</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>China PR Super League</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>08:35:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Beijing Guoan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Shandong Taishan</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>China PR Super League</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tianjin Jinmen Tiger</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Shenzhen Peng City</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>77</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finland Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Finland Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finland Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finland Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mariehamn</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Hødd</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Västerås SK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ÍA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>99</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B22" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>83</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>95-100%</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>92.60000000000001</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -559,16 +1548,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1424</v>
+        <v>1462</v>
       </c>
       <c r="C2" t="n">
-        <v>1416</v>
+        <v>1451</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.44</v>
+        <v>99.25</v>
       </c>
     </row>
     <row r="3">
@@ -578,16 +1567,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C3" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>96.44</v>
+        <v>95.93000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -597,16 +1586,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>90.14</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="5">
@@ -616,16 +1605,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="6">
@@ -635,10 +1624,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -654,10 +1643,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -673,10 +1662,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -768,13 +1757,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -787,13 +1776,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -806,13 +1795,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -825,13 +1814,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,12 +484,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93.60000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C2" t="n">
         <v>1438</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="3">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C3" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>97.08</v>
+        <v>98.06</v>
       </c>
     </row>
     <row r="4">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>95.08</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="5">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,43 +471,516 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>China PR Super League</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08:35:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Shandong Taishan</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yunnan Yukun</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Finland Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>94</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Waterford United</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>St Patrick's</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wexford Youths</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B11" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>75-80%</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -559,16 +1032,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1450</v>
+        <v>1431</v>
       </c>
       <c r="C2" t="n">
-        <v>1438</v>
+        <v>1424</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>99.17</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -578,16 +1051,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C3" t="n">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>98.06</v>
+        <v>97.31999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -597,16 +1070,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>94.19</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="5">
@@ -616,16 +1089,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="6">
@@ -638,13 +1111,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -654,10 +1127,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -673,16 +1146,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -692,16 +1165,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -711,16 +1184,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -768,13 +1241,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -787,13 +1260,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -806,13 +1279,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -825,13 +1298,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shandong Taishan</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>96.8</v>
+        <v>86</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.39999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>94</v>
+        <v>97.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Waterford United</t>
+          <t>Tianjin Jinmen Tiger</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95.19999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>Shanghai Port</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95.19999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>95</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,25 +729,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>99.2</v>
+        <v>93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>98.2</v>
+        <v>96.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -815,25 +815,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>98.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,36 +890,36 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bodø / Glimt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,54 +933,699 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>89.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>97</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Uruguay Primera Division</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Deportivo Maldonado</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Albion</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="B22" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>93</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KR Reykjavík</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>KA Akureyri</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ÍA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>17:05:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -1032,16 +1677,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1431</v>
+        <v>1524</v>
       </c>
       <c r="C2" t="n">
-        <v>1424</v>
+        <v>1508</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>99.51000000000001</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="3">
@@ -1051,16 +1696,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="C3" t="n">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>97.31999999999999</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1070,16 +1715,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>97.62</v>
+        <v>86.95999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1089,16 +1734,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -1108,10 +1753,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1146,16 +1791,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1184,13 +1829,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1279,13 +1924,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1298,13 +1943,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1317,13 +1962,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,11 +471,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,12 +484,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>99.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>97.8</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,11 +589,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>93</v>
+        <v>97.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>CF Montréal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,11 +675,140 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>79.60000000000001</v>
+        <v>97</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>90.60000000000001</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>99</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -731,16 +860,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1471</v>
+        <v>1503</v>
       </c>
       <c r="C2" t="n">
-        <v>1461</v>
+        <v>1488</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>99.31999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -750,16 +879,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="C3" t="n">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>98.59999999999999</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -769,16 +898,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>96.43000000000001</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="5">
@@ -788,16 +917,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.55</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -807,10 +936,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -826,10 +955,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -864,16 +993,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -940,13 +1069,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -959,13 +1088,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -997,13 +1126,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -479,22 +479,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 x 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -522,17 +522,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>97.39999999999999</v>
+        <v>99</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>97.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95.19999999999999</v>
+        <v>90</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF Montréal</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>97</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Shanghai Port</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90.60000000000001</v>
+        <v>98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,41 +772,600 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>98</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bodø / Glimt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>84.39999999999999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>97</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>USA Major League Soccer</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="B21" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21:10:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Atlanta United</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23:25:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -860,16 +1419,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1503</v>
+        <v>1508</v>
       </c>
       <c r="C2" t="n">
-        <v>1488</v>
+        <v>1499</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -879,16 +1438,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C3" t="n">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>97.76000000000001</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -898,16 +1457,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>96.59</v>
+        <v>93.42</v>
       </c>
     </row>
     <row r="5">
@@ -917,16 +1476,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -939,13 +1498,13 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +1514,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -974,10 +1533,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -993,16 +1552,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1012,13 +1571,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1069,13 +1628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1088,13 +1647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1107,13 +1666,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1126,13 +1685,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 x 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>98</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>99</v>
+        <v>94.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Qingdao West Coast</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>88.40000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Liaoning Tieren FC</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>94.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shanghai Port</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>98</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,25 +729,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>96</v>
+        <v>97.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,25 +772,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bodø / Glimt</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,527 +847,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>98.8</v>
+        <v>83</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Uruguay Primera Division</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Albion</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Juventud</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>84.39999999999999</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>80-85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Uruguay Primera Division</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>19:30:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Wanderers</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>97</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>89.60000000000001</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>19:30:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bragantino</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>21:10:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Atlanta United</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>23:25:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>95.19999999999999</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -1419,16 +903,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="C2" t="n">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99.40000000000001</v>
+        <v>99.34</v>
       </c>
     </row>
     <row r="3">
@@ -1438,16 +922,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="C3" t="n">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>97.34999999999999</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="4">
@@ -1457,16 +941,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C4" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>93.42</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1476,10 +960,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1495,16 +979,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>95.45</v>
       </c>
     </row>
     <row r="7">
@@ -1514,16 +998,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -1647,13 +1131,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1666,13 +1150,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93.60000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Ulsan HD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.8</v>
+        <v>96.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>95.19999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -613,12 +613,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>95.19999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>97.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:35:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,54 +804,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Uruguay Primera Division</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Defensor Sporting</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>83</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>80-85%</t>
+          <t>70-75%</t>
         </is>
       </c>
     </row>
@@ -903,16 +860,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1504</v>
+        <v>1547</v>
       </c>
       <c r="C2" t="n">
-        <v>1494</v>
+        <v>1537</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99.34</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -925,13 +882,13 @@
         <v>355</v>
       </c>
       <c r="C3" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>98.03</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="4">
@@ -941,16 +898,16 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" t="n">
         <v>92</v>
       </c>
-      <c r="C4" t="n">
-        <v>88</v>
-      </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>95.65000000000001</v>
+        <v>91.09</v>
       </c>
     </row>
     <row r="5">
@@ -960,10 +917,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -979,16 +936,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>95.45</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -998,16 +955,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1017,10 +974,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1036,13 +993,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1112,13 +1069,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1131,13 +1088,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1150,13 +1107,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1169,13 +1126,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -479,22 +479,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>21:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 x 0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>90.8</v>
+        <v>60.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>60-65%</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -527,12 +527,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ulsan HD</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96.8</v>
+        <v>79.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -570,12 +570,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>75.8</v>
+        <v>91.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.19999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>97.8</v>
+        <v>93.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bodø / Glimt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>91.8</v>
+        <v>99.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -742,12 +742,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -776,21 +776,21 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:35:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,11 +804,914 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>70.39999999999999</v>
+        <v>97</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>97</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Athletico PR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New England</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Atlanta United</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>92.60000000000001</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CF Montréal</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>92</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -860,16 +1763,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C2" t="n">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.34999999999999</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -879,16 +1782,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C3" t="n">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>97.75</v>
+        <v>97.13</v>
       </c>
     </row>
     <row r="4">
@@ -898,16 +1801,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>91.09</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -917,16 +1820,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="6">
@@ -936,16 +1839,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +1858,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -974,10 +1877,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -996,13 +1899,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1012,16 +1915,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1069,13 +1972,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1088,13 +1991,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1107,13 +2010,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1126,13 +2029,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1145,13 +2048,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,26 +475,26 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:35:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 x 0</t>
+          <t>1 x 0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,18 +503,18 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60.6</v>
+        <v>94.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -522,22 +522,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimcheon Sangmu</t>
+          <t>Athletico PR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,18 +546,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.2</v>
+        <v>92.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -565,22 +565,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>91.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -608,22 +608,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -632,18 +632,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>87.8</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -651,22 +651,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlanta United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 x 0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93.8</v>
+        <v>86.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -694,22 +694,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>99.8</v>
+        <v>98.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -737,17 +737,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>97</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -780,22 +780,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CF Montréal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>97</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -823,17 +823,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,18 +847,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>89.60000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -866,17 +866,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>96.39999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,18 +933,18 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>94.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -952,17 +952,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athletico PR</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,18 +976,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -995,17 +995,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,18 +1019,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>94.19999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,36 +1062,36 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>75.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,36 +1105,36 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>96.2</v>
+        <v>85.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,36 +1148,36 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>95.39999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,36 +1191,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>98.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>96.2</v>
+        <v>99.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>New England</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,36 +1277,36 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>83.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlanta United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,36 +1320,36 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>92.60000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>99.40000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1374,11 +1374,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1406,312 +1406,11 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>95.19999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CF Montréal</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>95.39999999999999</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Orlando City</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>USA Major League Soccer</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>92</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
@@ -1763,16 +1462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1546</v>
+        <v>1564</v>
       </c>
       <c r="C2" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="3">
@@ -1782,16 +1481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C3" t="n">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>97.13</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="4">
@@ -1801,16 +1500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>95.40000000000001</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="5">
@@ -1820,16 +1519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>97.06</v>
+        <v>96.43000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1839,16 +1538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1858,10 +1557,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1880,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -1896,16 +1595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1915,16 +1614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1972,13 +1671,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1991,13 +1690,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2010,13 +1709,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2029,13 +1728,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2048,13 +1747,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:45:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1 x 0</t>
+          <t>1 x 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,41 +503,41 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>94.8</v>
+        <v>88</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletico PR</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 x 0</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>92.2</v>
+        <v>94</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,11 +557,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -570,17 +570,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0 x 1</t>
+          <t>2 x 0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,41 +589,41 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>94.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0 x 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -632,41 +632,41 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>82.19999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atlanta United</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,41 +675,41 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>86.2</v>
+        <v>99.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>98.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>95.39999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,30 +772,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CF Montréal</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>98.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>92.2</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>St Patrick's</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>99.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Rubio Ñú</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>94.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -944,25 +944,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,36 +976,36 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>99.59999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Gimnasia y Esgrima Mendoza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Central Cordoba SdE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,36 +1019,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>98.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>65-70%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>93.8</v>
+        <v>92.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1077,21 +1077,21 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>85.8</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>91.40000000000001</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:05:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Deportes Quindío</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>97.59999999999999</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1288,25 +1288,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,36 +1320,36 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>96.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>95.19999999999999</v>
+        <v>96</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1406,11 +1406,11 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>80.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1564</v>
+        <v>1541</v>
       </c>
       <c r="C2" t="n">
-        <v>1555</v>
+        <v>1533</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>99.42</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="3">
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="C3" t="n">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>97.2</v>
+        <v>97.70999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>92.13</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="5">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.43000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="6">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>22:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1 x 1</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,41 +503,41 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>06:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Tianjin Jinmen Tiger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>91.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,30 +557,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Shanghai Port</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>84.2</v>
+        <v>96.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>85.8</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Chongqing Tonglianglong FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>99.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>98.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>90.2</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -858,25 +858,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>St Patrick's</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>97.8</v>
+        <v>98</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rubio Ñú</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,36 +933,36 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,36 +976,36 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94.19999999999999</v>
+        <v>86</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima Mendoza</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Central Cordoba SdE</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,36 +1019,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>68.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Waterford United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,36 +1062,36 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>92.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,36 +1105,36 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>84.39999999999999</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,36 +1148,36 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>92.80000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,36 +1191,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>89.2</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Estudiantes de Río Cuarto</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,36 +1234,36 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>99.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:05:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportes Quindío</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,36 +1277,36 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>95.39999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,36 +1320,36 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>81.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Llaneros</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,52 +1363,1170 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>96</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Wexford Youths</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>94</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>97</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Unión Magdalena</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>93</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Real San Andres</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>89</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Colombia Liga BetPlay</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B29" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>18:05:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>72</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>22:15:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Jaguares de Córdoba</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Junior FC</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Athletico PR</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>97</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>96</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>94</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>93</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:15:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>88</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CF Montréal</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>98</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New England</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Atlanta United</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>90</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -1462,16 +2580,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1541</v>
+        <v>1611</v>
       </c>
       <c r="C2" t="n">
-        <v>1533</v>
+        <v>1603</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>99.48</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3">
@@ -1481,16 +2599,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C3" t="n">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>97.70999999999999</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1500,16 +2618,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>96.59</v>
+        <v>88.31</v>
       </c>
     </row>
     <row r="5">
@@ -1519,16 +2637,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1538,16 +2656,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="7">
@@ -1557,10 +2675,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1579,13 +2697,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1595,16 +2713,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1614,16 +2732,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1671,13 +2789,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1690,13 +2808,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1709,13 +2827,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1728,13 +2846,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1747,13 +2865,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22:15:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0 x 0</t>
+          <t>0 x 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -522,17 +522,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,18 +546,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>91.2</v>
+        <v>82</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -565,22 +565,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shanghai Port</t>
+          <t>Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,18 +589,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>96.8</v>
+        <v>94</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -608,17 +608,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Liaoning Tieren FC</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao West Coast</t>
+          <t>Real San Andres</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,18 +632,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95.39999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -651,22 +651,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong FC</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -694,22 +694,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>18:05:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gimcheon Sangmu</t>
+          <t>Independiente Medellín</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 x 2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -718,18 +718,18 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90.8</v>
+        <v>74.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>70-75%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -737,17 +737,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,18 +761,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>87.2</v>
+        <v>97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -780,17 +780,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>22:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Junior FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,18 +804,18 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>97.39999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -823,22 +823,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Athletico PR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>96.39999999999999</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -866,22 +866,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,18 +933,18 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>84.2</v>
+        <v>94</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -952,17 +952,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>86</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -995,17 +995,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,18 +1019,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>93.8</v>
+        <v>84</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CF Montréal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>96.59999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,18 +1105,18 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>97.39999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,18 +1148,18 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>97.8</v>
+        <v>89</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>92.80000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto</t>
+          <t>New England</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Atlanta United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,18 +1234,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>87.40000000000001</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1253,17 +1253,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>85.8</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,18 +1320,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>97.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,18 +1363,18 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>82.19999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1382,17 +1382,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1406,18 +1406,18 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>98.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>95.8</v>
+        <v>96</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>97</v>
+        <v>96.2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Unión Magdalena</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1535,18 +1535,18 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>93</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real San Andres</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1578,36 +1578,36 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>86.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ulsan HD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1632,25 +1632,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:05:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1664,36 +1664,36 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>72</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1707,36 +1707,36 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>97.39999999999999</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:15:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Junior FC</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1750,36 +1750,36 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>91.8</v>
+        <v>81.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Athletico PR</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1793,36 +1793,36 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>97</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1847,25 +1847,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1879,36 +1879,36 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>94</v>
+        <v>87.2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1922,36 +1922,36 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>93</v>
+        <v>85.39999999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1965,36 +1965,36 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CF Montréal</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>95.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Zhejiang</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2051,36 +2051,36 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>89.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2094,36 +2094,36 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>87.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2137,36 +2137,36 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>98</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>New England</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlanta United</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>95.8</v>
+        <v>99.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2223,36 +2223,36 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>90</v>
+        <v>97.8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2266,36 +2266,36 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>91.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2309,36 +2309,36 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>96.39999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>96.39999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>97.39999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2406,25 +2406,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2438,36 +2438,36 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>87.8</v>
+        <v>91</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Bodø / Glimt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2481,36 +2481,36 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>97.2</v>
+        <v>90.2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2524,9 +2524,1342 @@
         </is>
       </c>
       <c r="H49" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Aalesund</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Åsane</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Strømmen</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Odd</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ranheim</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>79.80000000000001</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>95</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>91</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>99</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>92</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
         <v>97.8</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>18:05:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>22:15:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Olimpia</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Guaraní</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ÍA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Patriotas Boyacá</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Internacional Palmira</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -2580,16 +3913,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C2" t="n">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.5</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2599,16 +3932,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C3" t="n">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>96.09999999999999</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="4">
@@ -2618,16 +3951,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>88.31</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="5">
@@ -2637,16 +3970,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="6">
@@ -2659,13 +3992,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +4008,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2713,10 +4046,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2808,13 +4141,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2827,13 +4160,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2846,13 +4179,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alianza Petrolera</t>
+          <t>Atlético</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0 x 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>92.60000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,22 +546,22 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>97.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -570,12 +570,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>94.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Rubio Ñú</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>96.8</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>82</v>
+        <v>96.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>81.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>Gimnasia y Esgrima Mendoza</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93.2</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,25 +772,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>94.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -815,25 +815,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Estudiantes de Río Cuarto</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>89.60000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Cundinamarca</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>95.8</v>
+        <v>99.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atlético</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>83.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -948,21 +948,21 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:35:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>85.39999999999999</v>
+        <v>89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -987,25 +987,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>95.39999999999999</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,11 +1062,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>83.59999999999999</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1662</v>
+        <v>1641</v>
       </c>
       <c r="C2" t="n">
-        <v>1653</v>
+        <v>1628</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>99.45999999999999</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C3" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>95.53</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="4">
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>97.59</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="5">
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="6">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atlético</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,18 +503,18 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>85.2</v>
+        <v>91.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -522,17 +522,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Estudiantes de Río Cuarto</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,18 +546,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>79.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -565,17 +565,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>21:35:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,18 +589,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>99.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -608,17 +608,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rubio Ñú</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>96.39999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -651,17 +651,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>96.2</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -690,21 +690,21 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>92.40000000000001</v>
+        <v>69.19999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>65-70%</t>
         </is>
       </c>
     </row>
@@ -733,21 +733,21 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima Mendoza</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92.60000000000001</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -776,21 +776,21 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -819,21 +819,21 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>76.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sportivo Luqueño</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,36 +890,36 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>99.2</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -944,25 +944,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:35:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,11 +976,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>89</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -991,21 +991,21 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96.39999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,11 +1062,54 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>93.60000000000001</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>87</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -1118,16 +1161,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1641</v>
+        <v>1710</v>
       </c>
       <c r="C2" t="n">
-        <v>1628</v>
+        <v>1696</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>99.20999999999999</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1137,16 +1180,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C3" t="n">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>96.95</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1156,16 +1199,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>93.27</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="5">
@@ -1175,16 +1218,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>93.75</v>
+        <v>96.43000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1194,10 +1237,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1232,16 +1275,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1251,16 +1294,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1327,13 +1370,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1346,13 +1389,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1365,13 +1408,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +475,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,41 +503,41 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91.8</v>
+        <v>97.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,41 +546,41 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.2</v>
+        <v>96.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:35:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,11 +589,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>89.8</v>
+        <v>95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>99.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -647,21 +647,21 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>92.60000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>69.19999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>90.60000000000001</v>
+        <v>94</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -776,21 +776,21 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,11 +804,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>92.60000000000001</v>
+        <v>84</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
@@ -819,21 +819,21 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>94.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sportivo Luqueño</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94.19999999999999</v>
+        <v>92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Central Cordoba SdE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>91</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Athletico PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,11 +976,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94.19999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -991,21 +991,21 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,36 +1019,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>94.19999999999999</v>
+        <v>97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,54 +1062,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94.39999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>87</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -1161,10 +1118,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1710</v>
+        <v>1716</v>
       </c>
       <c r="C2" t="n">
-        <v>1696</v>
+        <v>1702</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -1180,16 +1137,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C3" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>95.54000000000001</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="4">
@@ -1199,16 +1156,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>93.06</v>
+        <v>91.01000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1218,16 +1175,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.43000000000001</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1237,10 +1194,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1256,16 +1213,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1275,16 +1232,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1294,10 +1251,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1370,13 +1327,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1389,13 +1346,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1408,13 +1365,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1427,13 +1384,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +475,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,41 +503,41 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>97.8</v>
+        <v>91</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Central Cordoba SdE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,26 +561,26 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 x 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>95</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,25 +600,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>86.8</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Bodø / Glimt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>94</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>84</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>81</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Central Cordoba SdE</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,36 +933,36 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>98.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athletico PR</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,36 +976,36 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>98.8</v>
+        <v>86.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Wexford Youths</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,54 +1019,355 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Real San Andres</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Patriotas Boyacá</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Unión Magdalena</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Colombia Liga BetPlay</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B21" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>85.39999999999999</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
@@ -1118,16 +1419,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1716</v>
+        <v>1698</v>
       </c>
       <c r="C2" t="n">
-        <v>1702</v>
+        <v>1686</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1137,16 +1438,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="C3" t="n">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>96.27</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="4">
@@ -1156,16 +1457,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>91.01000000000001</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="5">
@@ -1175,16 +1476,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.15000000000001</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -1194,10 +1495,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1213,16 +1514,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1232,10 +1533,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1251,10 +1552,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1346,13 +1647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1365,13 +1666,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1384,13 +1685,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Real San Andres</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Patriotas Boyacá</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91</v>
+        <v>94.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Central Cordoba SdE</t>
+          <t>Unión Magdalena</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>98</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>96.39999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Llaneros</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,18 +632,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93.60000000000001</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -651,17 +651,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Yingbo</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95.19999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -694,17 +694,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>91</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>96.39999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,25 +772,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>87.40000000000001</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>95.39999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -858,25 +858,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,36 +890,36 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94.59999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Varberg BoIS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,36 +933,36 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>88.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,36 +976,36 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>86.8</v>
+        <v>90.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,36 +1019,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>98.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1073,25 +1073,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Tianjin Jinmen Tiger</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>98.40000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real San Andres</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Patriotas Boyacá</t>
+          <t>Zhejiang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,36 +1148,36 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>92.80000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Unión Magdalena</t>
+          <t>Shanghai Port</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,36 +1191,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>98.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,36 +1234,36 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>75.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,36 +1277,36 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94.59999999999999</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,36 +1320,36 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>92.2</v>
+        <v>96.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,11 +1363,1516 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>85.39999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Piast Gliwice</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Wisła Kraków</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Wieczysta Kraków</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Häcken</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>97</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Iceland Pepsideild</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>96</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>91</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>92.60000000000001</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>94</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Unión Santa Fe</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>97</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>94</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>18:05:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22:15:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Junior FC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2 de Mayo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>95</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Boca Juniors de Cali</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tigres</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Atlanta United</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CF Montréal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>New England</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>99</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>97</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>86</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>23:45:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -1419,16 +2924,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1698</v>
+        <v>1712</v>
       </c>
       <c r="C2" t="n">
-        <v>1686</v>
+        <v>1702</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="3">
@@ -1438,16 +2943,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="C3" t="n">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>96.77</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="4">
@@ -1457,16 +2962,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>93.41</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -1476,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="6">
@@ -1495,16 +3000,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="7">
@@ -1533,16 +3038,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="9">
@@ -1552,16 +3057,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1628,13 +3133,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1647,13 +3152,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1666,13 +3171,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1685,13 +3190,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -479,17 +479,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Real San Andres</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Patriotas Boyacá</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>94.8</v>
+        <v>90</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,30 +514,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unión Magdalena</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>95.59999999999999</v>
+        <v>97</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,30 +557,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 x 0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>82.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -613,12 +613,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>97.39999999999999</v>
+        <v>94</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -647,26 +647,26 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>18:05:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Alianza Petrolera</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 x 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>90.40000000000001</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Independiente Medellín</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>88.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -737,17 +737,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>22:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Junior FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimcheon Sangmu</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,18 +761,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>97.59999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -780,22 +780,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Sportivo Luqueño</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 x 0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -804,18 +804,18 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>93.60000000000001</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -823,22 +823,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -866,17 +866,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,18 +890,18 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>95.19999999999999</v>
+        <v>92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Varberg BoIS</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>97.8</v>
+        <v>98.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -952,17 +952,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Atlanta United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,18 +976,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90.8</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -995,17 +995,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>98</v>
+        <v>96.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,18 +1105,18 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>95.19999999999999</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>CF Montréal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhejiang</t>
+          <t>New England</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>99.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shanghai Port</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Taishan</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>89.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,18 +1234,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>99.2</v>
+        <v>93.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1253,17 +1253,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,18 +1277,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>95.39999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,18 +1320,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>96.2</v>
+        <v>90</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,18 +1363,18 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>89.8</v>
+        <v>96</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1382,17 +1382,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1406,18 +1406,18 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>98.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>23:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>94.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1460,25 +1460,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1492,36 +1492,36 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1546,25 +1546,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Chongqing Tonglianglong FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1578,36 +1578,36 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>91</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1621,36 +1621,36 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>92.80000000000001</v>
+        <v>95</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1664,36 +1664,36 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>92.60000000000001</v>
+        <v>45</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>45-50%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Albion</t>
+          <t>Ulsan HD</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1707,36 +1707,36 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventud</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1750,36 +1750,36 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>90.2</v>
+        <v>98.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1804,25 +1804,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima Mendoza</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1836,36 +1836,36 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>91.60000000000001</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1890,25 +1890,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1933,25 +1933,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1965,36 +1965,36 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>94.39999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rionegro Águilas</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2008,36 +2008,36 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>18:05:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Alianza Petrolera</t>
+          <t>Waterford United</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2051,36 +2051,36 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>96.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>St Patrick's</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2094,36 +2094,36 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>89.2</v>
+        <v>96.2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>22:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Junior FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2137,36 +2137,36 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>97.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>70-75%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>95</v>
+        <v>97.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sportivo Luqueño</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2266,36 +2266,36 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>90.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>96.59999999999999</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2320,25 +2320,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlanta United</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2395,36 +2395,36 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>95.59999999999999</v>
+        <v>81.39999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2438,36 +2438,36 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>95.19999999999999</v>
+        <v>90</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2481,36 +2481,36 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>94.39999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2524,36 +2524,36 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>89.2</v>
+        <v>95.8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CF Montréal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New England</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2567,36 +2567,36 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>93.8</v>
+        <v>95</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2610,36 +2610,36 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Central Español</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2653,36 +2653,36 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>92.80000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlético Progreso</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2696,36 +2696,36 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>93.2</v>
+        <v>96</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2739,36 +2739,36 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>91.60000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2782,36 +2782,36 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>97</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>86</v>
+        <v>85.8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>23:45:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2868,11 +2868,398 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>93.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Olimpia</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Rubio Ñú</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Guaraní</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>17:45:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>19:45:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Real Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Internacional Palmira</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>97</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Atlético</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -2924,16 +3311,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1712</v>
+        <v>1659</v>
       </c>
       <c r="C2" t="n">
-        <v>1702</v>
+        <v>1651</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>99.42</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="3">
@@ -2943,16 +3330,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384</v>
+        <v>438</v>
       </c>
       <c r="C3" t="n">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>95.05</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="4">
@@ -2962,16 +3349,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>93.64</v>
       </c>
     </row>
     <row r="5">
@@ -2981,16 +3368,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>96.67</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -3000,16 +3387,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -3019,10 +3406,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -3041,13 +3428,13 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -3057,16 +3444,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -3133,13 +3520,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3152,16 +3539,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="15">
@@ -3171,13 +3558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3190,13 +3577,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3228,13 +3615,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +475,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>81.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Central Cordoba SdE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>88.8</v>
+        <v>89.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -565,17 +565,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Cúcuta Deportivo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>92.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,25 +600,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95.19999999999999</v>
+        <v>93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>91</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Independiente Medellín</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>96</v>
+        <v>99.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,25 +729,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,697 +761,9 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Cork City</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Athlone Town</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Norway Obos-Ligaen</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ranheim</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Haugesund</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sweden Allsvenskan</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Halmstad</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sirius</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sweden Allsvenskan</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Djurgården</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Västerås SK</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>93.60000000000001</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sweden Superettan</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14:05:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Värnamo</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>96</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Paraguay Division 1</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sportivo Trinidense</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sportivo San Lorenzo</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Paraguay Division 1</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Deportivo Recoleta</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Nacional Asunción</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>94</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Iceland Pepsideild</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>16:15:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Valur</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Stjarnan</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>91.60000000000001</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Argentina Superliga</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>16:45:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Sarmiento</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Independiente Rivadavia</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>85-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Argentina Superliga</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Platense</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Talleres Córdoba</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Argentina Superliga</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Vélez Sarsfield</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Independiente</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Argentina Superliga</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>21:15:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Huracán</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Atlético Tucumán</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>95.39999999999999</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Argentina Superliga</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>21:15:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Central Cordoba SdE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>San Lorenzo</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>92.80000000000001</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>90-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Colombia Torneo Betplay</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>17:30:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Independiente Yumbo</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Envigado</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Uruguay Primera Division</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Defensor Sporting</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Cerro</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Colombia Liga BetPlay</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Cúcuta Deportivo</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>98</v>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>95-100%</t>
         </is>
@@ -1505,16 +817,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1729</v>
+        <v>1662</v>
       </c>
       <c r="C2" t="n">
-        <v>1719</v>
+        <v>1656</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>99.42</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="3">
@@ -1524,16 +836,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>432</v>
+        <v>494</v>
       </c>
       <c r="C3" t="n">
-        <v>419</v>
+        <v>487</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>96.98999999999999</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="4">
@@ -1543,16 +855,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>93.27</v>
+        <v>95.33</v>
       </c>
     </row>
     <row r="5">
@@ -1562,16 +874,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>94.29000000000001</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="6">
@@ -1581,16 +893,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1600,10 +912,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1619,10 +931,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1638,16 +950,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1714,13 +1026,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1733,13 +1045,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1752,13 +1064,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1771,13 +1083,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1790,13 +1102,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>96.2</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,25 +514,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Central Cordoba SdE</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,36 +546,36 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>89.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo</t>
+          <t>KR Reykjavík</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>91.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93</v>
+        <v>75.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Llaneros</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93.40000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>99.2</v>
+        <v>95.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -733,21 +733,21 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22:20:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,11 +761,54 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>95.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -817,16 +860,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1662</v>
+        <v>1681</v>
       </c>
       <c r="C2" t="n">
-        <v>1656</v>
+        <v>1676</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>99.64</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="3">
@@ -836,16 +879,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="C3" t="n">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>98.58</v>
+        <v>97.48</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +898,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>95.33</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="5">
@@ -874,16 +917,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>97.56</v>
+        <v>95.45</v>
       </c>
     </row>
     <row r="6">
@@ -893,16 +936,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>94.73999999999999</v>
+        <v>95.23999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -912,16 +955,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +974,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -950,16 +993,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1045,13 +1088,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1064,13 +1107,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22:20:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>95.19999999999999</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -522,17 +522,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>América de Cali</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.59999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Iceland Pepsideild</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Cundinamarca</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KR Reykjavík</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>86.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,25 +600,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atlético</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Real San Andres</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>75.8</v>
+        <v>85.39999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,22 +675,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95.19999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -699,12 +699,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>95.8</v>
+        <v>90.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>22:10:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93.2</v>
+        <v>89</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>América de Cali</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,11 +804,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>92.80000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>70-75%</t>
         </is>
       </c>
     </row>
@@ -860,16 +860,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1681</v>
+        <v>1771</v>
       </c>
       <c r="C2" t="n">
-        <v>1676</v>
+        <v>1761</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>99.7</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="3">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>477</v>
+        <v>424</v>
       </c>
       <c r="C3" t="n">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>97.48</v>
+        <v>96.93000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -898,16 +898,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>98.31</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="5">
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>95.45</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="6">
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>96.39999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>22:10:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América de Cali</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,18 +546,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>94.19999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -565,22 +565,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Real Cundinamarca</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,36 +589,36 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>87.2</v>
+        <v>67.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>65-70%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>07:25:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlético</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real San Andres</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>85.39999999999999</v>
+        <v>96</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>86.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90.2</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>89</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -772,43 +772,731 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GIF Sundsvall</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Wexford Youths</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>85</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rubio Ñú</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>88</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Argentina Superliga</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Unión Santa Fe</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Lanús</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>70-75%</t>
+      <c r="B21" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:45:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Colombia Torneo Betplay</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Deportes Quindío</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Internacional Palmira</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
@@ -860,16 +1548,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1771</v>
+        <v>1727</v>
       </c>
       <c r="C2" t="n">
-        <v>1761</v>
+        <v>1720</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>99.44</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="3">
@@ -879,16 +1567,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="C3" t="n">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>96.93000000000001</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="4">
@@ -898,16 +1586,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>92.78</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="5">
@@ -917,16 +1605,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>94.12</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="6">
@@ -936,10 +1624,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -955,10 +1643,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -974,10 +1662,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -993,10 +1681,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1088,13 +1776,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1107,13 +1795,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1126,13 +1814,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1145,13 +1833,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Rubio Ñú</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 x 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>89.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:10:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Cerro Largo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Juventud</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>87.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,26 +561,26 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0 x 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,18 +589,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>67.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -608,17 +608,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07:25:00</t>
+          <t>21:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Estudiantes de Río Cuarto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,18 +632,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -651,17 +651,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>90.2</v>
+        <v>97</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -694,17 +694,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenzhen Peng City</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,18 +718,18 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>82.39999999999999</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Colombia Torneo Betplay</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -737,17 +737,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Deportes Quindío</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Internacional Palmira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>86.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>95.8</v>
+        <v>95</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -815,25 +815,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>97.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>97.2</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>FC Tokyo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,36 +933,36 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>97.39999999999999</v>
+        <v>78.60000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,36 +976,36 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>92.80000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Japan J-League</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>07:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford Youths</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96.2</v>
+        <v>97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,36 +1062,36 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>99.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,36 +1105,36 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>85</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>96.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1159,25 +1159,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,36 +1191,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>80.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rubio Ñú</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95.19999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Zhejiang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventud</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,36 +1277,36 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,36 +1320,36 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>89.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,36 +1363,36 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>91.60000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ulsan HD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1406,36 +1406,36 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>96.39999999999999</v>
+        <v>86</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1449,54 +1449,1430 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>96.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>Korea Republic K-League 1</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gimcheon Sangmu</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Korea Republic K-League 1</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>66.60000000000001</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Korea Republic K-League 1</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>88</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bodø / Glimt</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Örgryte</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Norway Obos-Ligaen</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Stabæk</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Atlético Progreso</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Uruguay Primera Division</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Finland Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>90</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>84</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>92.60000000000001</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>94</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Deportes Quindío</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Internacional Palmira</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Platense</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>97</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Argentina Superliga</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>97</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>93</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>18:20:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20:25:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Colombia Liga BetPlay</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>95</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Paraguay Division 1</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2 de Mayo</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Olimpia</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>95-100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>New England</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -1548,16 +2924,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="C2" t="n">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>99.59</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="3">
@@ -1567,16 +2943,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="C3" t="n">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>97.09</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="4">
@@ -1586,16 +2962,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>97.27</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="5">
@@ -1605,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
         <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>91.3</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="6">
@@ -1624,10 +3000,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1681,16 +3057,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1757,13 +3133,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1776,13 +3152,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1795,13 +3171,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1814,13 +3190,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1833,13 +3209,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/resultado_saiu_gol.xlsx
+++ b/resultado_saiu_gol.xlsx
@@ -471,30 +471,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rubio Ñú</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0 x 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,36 +503,36 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>96</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventud</t>
+          <t>Gimnasia y Esgrima Mendoza</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>89.2</v>
+        <v>86</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,25 +557,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>85.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,25 +600,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,36 +632,36 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>91.60000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:25:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -686,25 +686,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -718,36 +718,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>97.39999999999999</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia Torneo Betplay</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deportes Quindío</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Internacional Palmira</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -761,36 +761,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>94.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Chongqing Tonglianglong FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Shanghai Port</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>China PR Super League</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Tianjin Jinmen Tiger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -847,36 +847,36 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>93.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -901,25 +901,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -933,36 +933,36 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>78.60000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>75-80%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -976,36 +976,36 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>99.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Japan J-League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>07:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,36 +1019,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>70-75%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,36 +1062,36 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94.59999999999999</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1105,36 +1105,36 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90.60000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>95.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1159,25 +1159,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,36 +1191,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>99.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1234,36 +1234,36 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>96.59999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zhejiang</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1277,36 +1277,36 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dalian Yingbo</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liaoning Tieren FC</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1331,25 +1331,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>China PR Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Varberg BoIS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1363,36 +1363,36 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>81.2</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>75-80%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Waterford United</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulsan HD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1406,36 +1406,36 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>86</v>
+        <v>91.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>St Patrick's</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>92.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1460,25 +1460,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gimcheon Sangmu</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>85.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1535,36 +1535,36 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>66.60000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Korea Republic K-League 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1578,36 +1578,36 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>88</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bodø / Glimt</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1621,36 +1621,36 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>88.59999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Athletico PR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1664,36 +1664,36 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>98.2</v>
+        <v>91.2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>91.8</v>
+        <v>94</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1718,25 +1718,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1750,36 +1750,36 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>96.39999999999999</v>
+        <v>94</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1793,36 +1793,36 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>97.39999999999999</v>
+        <v>85</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Norway Obos-Ligaen</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1836,36 +1836,36 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>99.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguay Primera Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Central Español</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Progreso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>94.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1894,21 +1894,21 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Albion</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>87.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
@@ -1937,21 +1937,21 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1965,36 +1965,36 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>85.8</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Uruguay Primera Division</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FC Den Bosch</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>92.80000000000001</v>
+        <v>94</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2051,36 +2051,36 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>97.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2094,36 +2094,36 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>90</v>
+        <v>97.8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2137,36 +2137,36 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>84</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2180,36 +2180,36 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>92.60000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>94</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Norway Obos-Ligaen</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2266,36 +2266,36 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97</v>
+        <v>91.8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Argentina Superliga</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima Mendoza</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2309,36 +2309,36 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>87.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>85-90%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>93.60000000000001</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>97</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2406,25 +2406,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2438,36 +2438,36 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>83.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Pepsideild</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2481,36 +2481,36 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>93</v>
+        <v>98.2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>95-100%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2524,36 +2524,36 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>91.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2567,36 +2567,36 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>92.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Boyacá Chicó</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2610,36 +2610,36 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>94.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Argentina Superliga</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>18:20:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2653,36 +2653,36 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>94.39999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>85-90%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>20:25:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Sportivo Luqueño</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>97.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Colombia Liga BetPlay</t>
+          <t>Paraguay Division 1</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2739,36 +2739,36 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>84.2</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>80-85%</t>
+          <t>90-95%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:05:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Alianza Petrolera</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2793,25 +2793,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Paraguay Division 1</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>98.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>USA Major League Soccer</t>
+          <t>Colombia Liga BetPlay</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>22:15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>New England</t>
+          <t>América de Cali</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>93.8</v>
+        <v>94.8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2924,16 +2924,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1723</v>
+        <v>1775</v>
       </c>
       <c r="C2" t="n">
-        <v>1719</v>
+        <v>1767</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>99.77</v>
+        <v>99.55</v>
       </c>
     </row>
     <row r="3">
@@ -2943,16 +2943,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C3" t="n">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>96.97</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="4">
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>93.91</v>
+        <v>90.98999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>93.33</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="6">
@@ -3000,16 +3000,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="7">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3152,13 +3152,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
